--- a/output/Tables/7000 steps/HIA_sex_7000steps_1000replicate.xlsx
+++ b/output/Tables/7000 steps/HIA_sex_7000steps_1000replicate.xlsx
@@ -438,22 +438,22 @@
         </is>
       </c>
       <c r="C2">
-        <v>60751.405</v>
+        <v>66179.08500000001</v>
       </c>
       <c r="D2">
-        <v>57799.498</v>
+        <v>63008.609</v>
       </c>
       <c r="E2">
-        <v>63698.838</v>
+        <v>69349.007</v>
       </c>
       <c r="F2">
-        <v>708656.514</v>
+        <v>710837.33</v>
       </c>
       <c r="G2">
-        <v>691036.358</v>
+        <v>693520.907</v>
       </c>
       <c r="H2">
-        <v>726512.481</v>
+        <v>728258.273</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>94290489205.98599</v>
+        <v>94545554137.683</v>
       </c>
       <c r="M2">
-        <v>91919122135.32201</v>
+        <v>92224493507.45799</v>
       </c>
       <c r="N2">
-        <v>96545238264.59399</v>
+        <v>96855707566.048</v>
       </c>
     </row>
     <row r="3">
@@ -486,22 +486,22 @@
         </is>
       </c>
       <c r="C3">
-        <v>98269.045</v>
+        <v>100987.075</v>
       </c>
       <c r="D3">
-        <v>93589.66</v>
+        <v>96087.382</v>
       </c>
       <c r="E3">
-        <v>102882.938</v>
+        <v>105857.195</v>
       </c>
       <c r="F3">
-        <v>943060.225</v>
+        <v>927439.997</v>
       </c>
       <c r="G3">
-        <v>915142.318</v>
+        <v>900134.25</v>
       </c>
       <c r="H3">
-        <v>972480.483</v>
+        <v>954768.586</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,13 +513,13 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>125553485130.757</v>
+        <v>123343195941.606</v>
       </c>
       <c r="M3">
-        <v>121751974142.283</v>
+        <v>119707968473.007</v>
       </c>
       <c r="N3">
-        <v>129167491136.962</v>
+        <v>127009606362.069</v>
       </c>
     </row>
     <row r="4">
@@ -534,40 +534,40 @@
         </is>
       </c>
       <c r="C4">
-        <v>62612.603</v>
+        <v>58458.998</v>
       </c>
       <c r="D4">
-        <v>60414.125</v>
+        <v>56430.17</v>
       </c>
       <c r="E4">
-        <v>64775.333</v>
+        <v>60484.138</v>
       </c>
       <c r="F4">
-        <v>63180.08</v>
+        <v>83650.40300000001</v>
       </c>
       <c r="G4">
-        <v>61385.88</v>
+        <v>81122.436</v>
       </c>
       <c r="H4">
-        <v>65042.957</v>
+        <v>86170.389</v>
       </c>
       <c r="I4">
-        <v>3485708912.419</v>
+        <v>3080628110.88</v>
       </c>
       <c r="J4">
-        <v>3364974770.587</v>
+        <v>2973598419.469</v>
       </c>
       <c r="K4">
-        <v>3613631264.812</v>
+        <v>3188165559.697</v>
       </c>
       <c r="L4">
-        <v>8394594598.586</v>
+        <v>11126662443.476</v>
       </c>
       <c r="M4">
-        <v>8141927165.009</v>
+        <v>10790130751.699</v>
       </c>
       <c r="N4">
-        <v>8645511359.671</v>
+        <v>11464122394.366</v>
       </c>
     </row>
     <row r="5">
@@ -582,40 +582,40 @@
         </is>
       </c>
       <c r="C5">
-        <v>83179.376</v>
+        <v>75148.662</v>
       </c>
       <c r="D5">
-        <v>79961.166</v>
+        <v>72283.345</v>
       </c>
       <c r="E5">
-        <v>86249.518</v>
+        <v>78022.503</v>
       </c>
       <c r="F5">
-        <v>67467.183</v>
+        <v>98165.489</v>
       </c>
       <c r="G5">
-        <v>65268.108</v>
+        <v>94672.57000000001</v>
       </c>
       <c r="H5">
-        <v>69886.817</v>
+        <v>101688.823</v>
       </c>
       <c r="I5">
-        <v>4630403270.974</v>
+        <v>3959778547.008</v>
       </c>
       <c r="J5">
-        <v>4452535433.638</v>
+        <v>3809300125.767</v>
       </c>
       <c r="K5">
-        <v>4804802517.704</v>
+        <v>4111700292.679</v>
       </c>
       <c r="L5">
-        <v>8974495831.974001</v>
+        <v>13054175597.078</v>
       </c>
       <c r="M5">
-        <v>8655712010.826</v>
+        <v>12592169048.296</v>
       </c>
       <c r="N5">
-        <v>9281543251.222</v>
+        <v>13521197802.072</v>
       </c>
     </row>
     <row r="6">
@@ -630,40 +630,40 @@
         </is>
       </c>
       <c r="C6">
-        <v>79497.696</v>
+        <v>12883.547</v>
       </c>
       <c r="D6">
-        <v>76975.15399999999</v>
+        <v>12493.105</v>
       </c>
       <c r="E6">
-        <v>81968.018</v>
+        <v>13274.841</v>
       </c>
       <c r="F6">
-        <v>141724.242</v>
+        <v>6793.735</v>
       </c>
       <c r="G6">
-        <v>136538.207</v>
+        <v>6594.967</v>
       </c>
       <c r="H6">
-        <v>147436.67</v>
+        <v>6993.833</v>
       </c>
       <c r="I6">
-        <v>1177370969.533</v>
+        <v>377752798.343</v>
       </c>
       <c r="J6">
-        <v>1138459968.013</v>
+        <v>366331995.432</v>
       </c>
       <c r="K6">
-        <v>1212132077.194</v>
+        <v>389153702.512</v>
       </c>
       <c r="L6">
-        <v>18843120924.833</v>
+        <v>903445008.473</v>
       </c>
       <c r="M6">
-        <v>18156559081.574</v>
+        <v>877118300.347</v>
       </c>
       <c r="N6">
-        <v>19624878215.546</v>
+        <v>930011398.524</v>
       </c>
     </row>
     <row r="7">
@@ -678,40 +678,40 @@
         </is>
       </c>
       <c r="C7">
-        <v>50151.391</v>
+        <v>16908.306</v>
       </c>
       <c r="D7">
-        <v>48317.097</v>
+        <v>16231.895</v>
       </c>
       <c r="E7">
-        <v>52192.65</v>
+        <v>17589.807</v>
       </c>
       <c r="F7">
-        <v>51287.64</v>
+        <v>7063.53</v>
       </c>
       <c r="G7">
-        <v>49147.809</v>
+        <v>6790.858</v>
       </c>
       <c r="H7">
-        <v>53318.015</v>
+        <v>7340.56</v>
       </c>
       <c r="I7">
-        <v>743285199.143</v>
+        <v>495713021.142</v>
       </c>
       <c r="J7">
-        <v>714367430.058</v>
+        <v>476058175.012</v>
       </c>
       <c r="K7">
-        <v>773071756.7180001</v>
+        <v>515633534.913</v>
       </c>
       <c r="L7">
-        <v>6821624226.478</v>
+        <v>939501734.982</v>
       </c>
       <c r="M7">
-        <v>6567004858.36</v>
+        <v>903119989.776</v>
       </c>
       <c r="N7">
-        <v>7108373037.777</v>
+        <v>976209933.045</v>
       </c>
     </row>
     <row r="8">
@@ -726,40 +726,40 @@
         </is>
       </c>
       <c r="C8">
-        <v>11901.236</v>
+        <v>8832.424000000001</v>
       </c>
       <c r="D8">
-        <v>11483.138</v>
+        <v>8575.18</v>
       </c>
       <c r="E8">
-        <v>12311.533</v>
+        <v>9092.651</v>
       </c>
       <c r="F8">
-        <v>25237.417</v>
+        <v>15699.902</v>
       </c>
       <c r="G8">
-        <v>24388.346</v>
+        <v>15245.021</v>
       </c>
       <c r="H8">
-        <v>26106.877</v>
+        <v>16159.461</v>
       </c>
       <c r="I8">
-        <v>894531293.6160001</v>
+        <v>346220314.794</v>
       </c>
       <c r="J8">
-        <v>863240066.918</v>
+        <v>336182145.006</v>
       </c>
       <c r="K8">
-        <v>927948191.572</v>
+        <v>356418421.54</v>
       </c>
       <c r="L8">
-        <v>3353400970.421</v>
+        <v>2088247429.36</v>
       </c>
       <c r="M8">
-        <v>3234893182.974</v>
+        <v>2027374812.837</v>
       </c>
       <c r="N8">
-        <v>3480221654.057</v>
+        <v>2149533378.589</v>
       </c>
     </row>
     <row r="9">
@@ -774,40 +774,40 @@
         </is>
       </c>
       <c r="C9">
-        <v>15824.23</v>
+        <v>11625.806</v>
       </c>
       <c r="D9">
-        <v>15275.661</v>
+        <v>11243.926</v>
       </c>
       <c r="E9">
-        <v>16407.652</v>
+        <v>12010.639</v>
       </c>
       <c r="F9">
-        <v>29357.053</v>
+        <v>21868.507</v>
       </c>
       <c r="G9">
-        <v>28180.37</v>
+        <v>21121.903</v>
       </c>
       <c r="H9">
-        <v>30522.208</v>
+        <v>22629.254</v>
       </c>
       <c r="I9">
-        <v>1189920004.667</v>
+        <v>455732743.562</v>
       </c>
       <c r="J9">
-        <v>1149051044.577</v>
+        <v>440755723.489</v>
       </c>
       <c r="K9">
-        <v>1233766501.987</v>
+        <v>470880922.889</v>
       </c>
       <c r="L9">
-        <v>3906944822.113</v>
+        <v>2908378342.864</v>
       </c>
       <c r="M9">
-        <v>3748896792.29</v>
+        <v>2808905124.263</v>
       </c>
       <c r="N9">
-        <v>4070462011.666</v>
+        <v>3008965439.883</v>
       </c>
     </row>
     <row r="10">
@@ -822,40 +822,40 @@
         </is>
       </c>
       <c r="C10">
-        <v>29276.299</v>
+        <v>28233.767</v>
       </c>
       <c r="D10">
-        <v>27821.278</v>
+        <v>26833.847</v>
       </c>
       <c r="E10">
-        <v>30812.406</v>
+        <v>29628.576</v>
       </c>
       <c r="F10">
-        <v>56568.581</v>
+        <v>32301.361</v>
       </c>
       <c r="G10">
-        <v>54347.467</v>
+        <v>30678.037</v>
       </c>
       <c r="H10">
-        <v>58665.644</v>
+        <v>33952.456</v>
       </c>
       <c r="I10">
-        <v>493976988.74</v>
+        <v>469971183.633</v>
       </c>
       <c r="J10">
-        <v>468058952.472</v>
+        <v>446862901.472</v>
       </c>
       <c r="K10">
-        <v>518875474.604</v>
+        <v>493248346.175</v>
       </c>
       <c r="L10">
-        <v>7520107897.102</v>
+        <v>4296453597.564</v>
       </c>
       <c r="M10">
-        <v>7249498820.644</v>
+        <v>4080714853.454</v>
       </c>
       <c r="N10">
-        <v>7785879478.612</v>
+        <v>4514649162.324</v>
       </c>
     </row>
     <row r="11">
@@ -870,40 +870,40 @@
         </is>
       </c>
       <c r="C11">
-        <v>21871.444</v>
+        <v>20028.267</v>
       </c>
       <c r="D11">
-        <v>20520.778</v>
+        <v>18839.793</v>
       </c>
       <c r="E11">
-        <v>23155.844</v>
+        <v>21241.481</v>
       </c>
       <c r="F11">
-        <v>25223.571</v>
+        <v>22918.111</v>
       </c>
       <c r="G11">
-        <v>24095.161</v>
+        <v>21513.94</v>
       </c>
       <c r="H11">
-        <v>26356.656</v>
+        <v>24333.452</v>
       </c>
       <c r="I11">
-        <v>368210016.791</v>
+        <v>333461387.668</v>
       </c>
       <c r="J11">
-        <v>345440453.563</v>
+        <v>313518941.385</v>
       </c>
       <c r="K11">
-        <v>390900753.294</v>
+        <v>353533527.633</v>
       </c>
       <c r="L11">
-        <v>3353538308.777</v>
+        <v>3047999004.524</v>
       </c>
       <c r="M11">
-        <v>3207134814.96</v>
+        <v>2861255766.661</v>
       </c>
       <c r="N11">
-        <v>3504350908.964</v>
+        <v>3236202761.805</v>
       </c>
     </row>
     <row r="12">
@@ -918,22 +918,22 @@
         </is>
       </c>
       <c r="C12">
-        <v>412439.618</v>
+        <v>294880.468</v>
       </c>
       <c r="D12">
-        <v>402802.083</v>
+        <v>287977.941</v>
       </c>
       <c r="E12">
-        <v>422541</v>
+        <v>301766.428</v>
       </c>
       <c r="F12">
-        <v>1259488.054</v>
+        <v>113045.123</v>
       </c>
       <c r="G12">
-        <v>1212718.211</v>
+        <v>109411.792</v>
       </c>
       <c r="H12">
-        <v>1303891.272</v>
+        <v>116694.594</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -945,13 +945,13 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>167454878033.672</v>
+        <v>15035317074.659</v>
       </c>
       <c r="M12">
-        <v>161778744898.865</v>
+        <v>14551939157.296</v>
       </c>
       <c r="N12">
-        <v>173492811660.481</v>
+        <v>15518204516.224</v>
       </c>
     </row>
     <row r="13">
@@ -966,22 +966,22 @@
         </is>
       </c>
       <c r="C13">
-        <v>204643.944</v>
+        <v>145005.711</v>
       </c>
       <c r="D13">
-        <v>199023.447</v>
+        <v>141047.595</v>
       </c>
       <c r="E13">
-        <v>210304.392</v>
+        <v>148949.928</v>
       </c>
       <c r="F13">
-        <v>529651.819</v>
+        <v>47607.7</v>
       </c>
       <c r="G13">
-        <v>508703.399</v>
+        <v>45832.686</v>
       </c>
       <c r="H13">
-        <v>550322.491</v>
+        <v>49400.527</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -993,13 +993,13 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>70505188149.707</v>
+        <v>6331740254.887</v>
       </c>
       <c r="M13">
-        <v>67875616422.336</v>
+        <v>6094385879.421</v>
       </c>
       <c r="N13">
-        <v>73165814843.049</v>
+        <v>6569976787.214</v>
       </c>
     </row>
   </sheetData>
